--- a/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_multi_source_sample.xlsx
+++ b/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_multi_source_sample.xlsx
@@ -1,36 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Fundamentals" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Schema stg_customers" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Relationships" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Quality" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Support" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Team" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Roles" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="SLA" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Servers" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Pricing" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Custom Properties" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="DET Models" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="DET Model Inputs" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="DET Sources" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="DET Source Schema" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="DET Mapping" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="DET Parameters" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="DET Relationships" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Operational Validation" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Operational Parameters" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="DET Lookups" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="DET Build" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="_DET Lists" sheetId="24" state="veryHidden" r:id="rId24"/>
-    <sheet name="_DET Metadata" sheetId="25" state="veryHidden" r:id="rId25"/>
-    <sheet name="_DET Context" sheetId="26" state="veryHidden" r:id="rId26"/>
-    <sheet name="_DET Raw ODCS" sheetId="27" state="veryHidden" r:id="rId27"/>
-    <sheet name="Schema customer_account_mart" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fundamentals" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schema stg_customers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quality" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLA" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Servers" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Custom Properties" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Models" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Model Inputs" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Sources" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Source Schema" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Mapping" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Parameters" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Relationships" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operational Validation" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operational Parameters" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Lookups" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Build" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_DET Lists" sheetId="24" state="veryHidden" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_DET Metadata" sheetId="25" state="veryHidden" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_DET Context" sheetId="26" state="veryHidden" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_DET Raw ODCS" sheetId="27" state="veryHidden" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schema customer_account_mart" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames>
     <definedName name="apiVersion">Fundamentals!$C$5</definedName>
@@ -132,33 +132,35 @@
     <definedName name="_DET_OP_clean_phone">'_DET Context'!$L$2:$L$2</definedName>
     <definedName name="_DET_OP_clean_text">'_DET Context'!$M$2:$M$5</definedName>
     <definedName name="_DET_OP_clean_timestamp">'_DET Context'!$N$2:$N$2</definedName>
-    <definedName name="_DET_OP_copy">'_DET Context'!$O$2:$O$2</definedName>
-    <definedName name="_DET_OP_correct_errors">'_DET Context'!$P$2:$P$3</definedName>
-    <definedName name="_DET_OP_fill_missing">'_DET Context'!$Q$2:$Q$2</definedName>
-    <definedName name="_DET_OP_is_between">'_DET Context'!$R$2:$R$5</definedName>
-    <definedName name="_DET_OP_is_email">'_DET Context'!$S$2:$S$2</definedName>
-    <definedName name="_DET_OP_is_in_list">'_DET Context'!$T$2:$T$4</definedName>
-    <definedName name="_DET_OP_is_positive">'_DET Context'!$U$2:$U$2</definedName>
-    <definedName name="_DET_OP_lower">'_DET Context'!$V$2:$V$2</definedName>
-    <definedName name="_DET_OP_map_values">'_DET Context'!$W$2:$W$10</definedName>
-    <definedName name="_DET_OP_no_future_date">'_DET Context'!$X$2:$X$2</definedName>
-    <definedName name="_DET_OP_regex_match">'_DET Context'!$Y$2:$Y$2</definedName>
-    <definedName name="_DET_OP_required">'_DET Context'!$Z$2:$Z$2</definedName>
-    <definedName name="_DET_OP_rule_compare">'_DET Context'!$AA$2:$AA$4</definedName>
-    <definedName name="_DET_OP_standardize_country">'_DET Context'!$AB$2:$AB$2</definedName>
-    <definedName name="_DET_OP_standardize_currency">'_DET Context'!$AC$2:$AC$2</definedName>
-    <definedName name="_DET_OP_title">'_DET Context'!$AD$2:$AD$2</definedName>
-    <definedName name="_DET_OP_unique">'_DET Context'!$AE$2:$AE$2</definedName>
-    <definedName name="_DET_OP_upper">'_DET Context'!$AF$2:$AF$2</definedName>
-    <definedName name="_DET_REL_customer_account_mart">'_DET Context'!$AG$2:$AG$12</definedName>
-    <definedName name="_DET_REL_raw_accounts">'_DET Context'!$AH$2:$AH$4</definedName>
-    <definedName name="_DET_REL_raw_customers">'_DET Context'!$AI$2:$AI$6</definedName>
-    <definedName name="_DET_REL_stg_customers">'_DET Context'!$AJ$2:$AJ$10</definedName>
-    <definedName name="_DET_VALUE_clean_code_case">'_DET Context'!$AK$2:$AK$4</definedName>
-    <definedName name="_DET_VALUE_clean_text_case">'_DET Context'!$AL$2:$AL$4</definedName>
-    <definedName name="_DET_VALUE_map_values_data_type">'_DET Context'!$AM$2:$AM$7</definedName>
-    <definedName name="_DET_VALUE_map_values_format_case">'_DET Context'!$AN$2:$AN$5</definedName>
-    <definedName name="_DET_VALUE_rule_compare_operator">'_DET Context'!$AO$2:$AO$8</definedName>
+    <definedName name="_DET_OP_convert_value">'_DET Context'!$O$2:$O$4</definedName>
+    <definedName name="_DET_OP_copy">'_DET Context'!$P$2:$P$2</definedName>
+    <definedName name="_DET_OP_correct_errors">'_DET Context'!$Q$2:$Q$3</definedName>
+    <definedName name="_DET_OP_fill_missing">'_DET Context'!$R$2:$R$2</definedName>
+    <definedName name="_DET_OP_is_between">'_DET Context'!$S$2:$S$5</definedName>
+    <definedName name="_DET_OP_is_email">'_DET Context'!$T$2:$T$2</definedName>
+    <definedName name="_DET_OP_is_in_list">'_DET Context'!$U$2:$U$4</definedName>
+    <definedName name="_DET_OP_is_positive">'_DET Context'!$V$2:$V$2</definedName>
+    <definedName name="_DET_OP_lower">'_DET Context'!$W$2:$W$2</definedName>
+    <definedName name="_DET_OP_map_values">'_DET Context'!$X$2:$X$10</definedName>
+    <definedName name="_DET_OP_no_future_date">'_DET Context'!$Y$2:$Y$2</definedName>
+    <definedName name="_DET_OP_regex_match">'_DET Context'!$Z$2:$Z$2</definedName>
+    <definedName name="_DET_OP_required">'_DET Context'!$AA$2:$AA$2</definedName>
+    <definedName name="_DET_OP_rule_compare">'_DET Context'!$AB$2:$AB$4</definedName>
+    <definedName name="_DET_OP_standardize_country">'_DET Context'!$AC$2:$AC$2</definedName>
+    <definedName name="_DET_OP_standardize_currency">'_DET Context'!$AD$2:$AD$2</definedName>
+    <definedName name="_DET_OP_title">'_DET Context'!$AE$2:$AE$2</definedName>
+    <definedName name="_DET_OP_unique">'_DET Context'!$AF$2:$AF$2</definedName>
+    <definedName name="_DET_OP_upper">'_DET Context'!$AG$2:$AG$2</definedName>
+    <definedName name="_DET_REL_customer_account_mart">'_DET Context'!$AH$2:$AH$12</definedName>
+    <definedName name="_DET_REL_raw_accounts">'_DET Context'!$AI$2:$AI$4</definedName>
+    <definedName name="_DET_REL_raw_customers">'_DET Context'!$AJ$2:$AJ$6</definedName>
+    <definedName name="_DET_REL_stg_customers">'_DET Context'!$AK$2:$AK$10</definedName>
+    <definedName name="_DET_VALUE_clean_code_case">'_DET Context'!$AL$2:$AL$4</definedName>
+    <definedName name="_DET_VALUE_clean_text_case">'_DET Context'!$AM$2:$AM$4</definedName>
+    <definedName name="_DET_VALUE_convert_value_data_type">'_DET Context'!$AN$2:$AN$7</definedName>
+    <definedName name="_DET_VALUE_map_values_data_type">'_DET Context'!$AO$2:$AO$7</definedName>
+    <definedName name="_DET_VALUE_map_values_format_case">'_DET Context'!$AP$2:$AP$5</definedName>
+    <definedName name="_DET_VALUE_rule_compare_operator">'_DET Context'!$AQ$2:$AQ$8</definedName>
     <definedName name="schema.businessName" localSheetId="2">'Schema stg_customers'!$B$8</definedName>
     <definedName name="schema.dataGranularityDescription" localSheetId="2">'Schema stg_customers'!$B$10</definedName>
     <definedName name="schema.description" localSheetId="2">'Schema stg_customers'!$B$7</definedName>
@@ -1038,69 +1040,9 @@
     <author>DET Compiler</author>
   </authors>
   <commentList>
-    <comment ref="F4" authorId="0" shapeId="0">
+    <comment ref="T13" authorId="0" shapeId="0">
       <text>
-        <t>Parameters: Remove Prefix, Remove Suffix, Case, Blank As Null</t>
-      </text>
-    </comment>
-    <comment ref="F5" authorId="0" shapeId="0">
-      <text>
-        <t>Parameters: Remove Prefix, Remove Suffix, Case, Blank As Null</t>
-      </text>
-    </comment>
-    <comment ref="F6" authorId="0" shapeId="0">
-      <text>
-        <t>Parameters: Trim, Collapse Whitespace, Case, Blank As Null</t>
-      </text>
-    </comment>
-    <comment ref="F7" authorId="0" shapeId="0">
-      <text>
-        <t>Parameters: none</t>
-      </text>
-    </comment>
-    <comment ref="F8" authorId="0" shapeId="0">
-      <text>
-        <t>Parameters: none</t>
-      </text>
-    </comment>
-    <comment ref="F9" authorId="0" shapeId="0">
-      <text>
-        <t>Parameters: Lookup, Default, Preserve Unmapped, Case Sensitive, Data Type, Precision, Scale, Format Pattern, Format Case</t>
-      </text>
-    </comment>
-    <comment ref="F10" authorId="0" shapeId="0">
-      <text>
-        <t>Parameters: none</t>
-      </text>
-    </comment>
-    <comment ref="F11" authorId="0" shapeId="0">
-      <text>
-        <t>Parameters: none</t>
-      </text>
-    </comment>
-    <comment ref="F12" authorId="0" shapeId="0">
-      <text>
-        <t>Parameters: none</t>
-      </text>
-    </comment>
-    <comment ref="F13" authorId="0" shapeId="0">
-      <text>
-        <t>Parameters: none</t>
-      </text>
-    </comment>
-    <comment ref="F14" authorId="0" shapeId="0">
-      <text>
-        <t>Parameters: none</t>
-      </text>
-    </comment>
-    <comment ref="F15" authorId="0" shapeId="0">
-      <text>
-        <t>Parameters: Trim, Collapse Whitespace, Case, Blank As Null</t>
-      </text>
-    </comment>
-    <comment ref="F16" authorId="0" shapeId="0">
-      <text>
-        <t>Parameters: Precision, Scale</t>
+        <t>Executable before DET Mapping steps. Enter one scalar SQL expression over fields from declared model inputs, for example UPPER(transaction_description). Do not enter SELECT, FROM, WHERE, joins, aliases, or multiple statements. det validate checks syntax using the configured adapter dialect and verifies column references.</t>
       </text>
     </comment>
   </commentList>
@@ -1108,6 +1050,94 @@
 </file>
 
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>DET Compiler</author>
+  </authors>
+  <commentList>
+    <comment ref="F4" authorId="0" shapeId="0">
+      <text>
+        <t>Parameters: Remove Prefix, Remove Suffix, Case, Blank As Null
+Recommended flow: convert_value/type-aware clean_* -&gt; standardize_*/correct_errors -&gt; mapping -&gt; fill_missing -&gt; derive/conform -&gt; validate/route -&gt; present. This is guidance, not a restriction. Do not use mapping format until the value has finished participating in semantic and business logic.</t>
+      </text>
+    </comment>
+    <comment ref="F5" authorId="0" shapeId="0">
+      <text>
+        <t>Parameters: Remove Prefix, Remove Suffix, Case, Blank As Null
+Recommended flow: convert_value/type-aware clean_* -&gt; standardize_*/correct_errors -&gt; mapping -&gt; fill_missing -&gt; derive/conform -&gt; validate/route -&gt; present. This is guidance, not a restriction. Do not use mapping format until the value has finished participating in semantic and business logic.</t>
+      </text>
+    </comment>
+    <comment ref="F6" authorId="0" shapeId="0">
+      <text>
+        <t>Parameters: Trim, Collapse Whitespace, Case, Blank As Null
+Recommended flow: convert_value/type-aware clean_* -&gt; standardize_*/correct_errors -&gt; mapping -&gt; fill_missing -&gt; derive/conform -&gt; validate/route -&gt; present. This is guidance, not a restriction. Do not use mapping format until the value has finished participating in semantic and business logic.</t>
+      </text>
+    </comment>
+    <comment ref="F7" authorId="0" shapeId="0">
+      <text>
+        <t>Parameters: none
+Recommended flow: convert_value/type-aware clean_* -&gt; standardize_*/correct_errors -&gt; mapping -&gt; fill_missing -&gt; derive/conform -&gt; validate/route -&gt; present. This is guidance, not a restriction. Do not use mapping format until the value has finished participating in semantic and business logic.</t>
+      </text>
+    </comment>
+    <comment ref="F8" authorId="0" shapeId="0">
+      <text>
+        <t>Parameters: none
+Recommended flow: convert_value/type-aware clean_* -&gt; standardize_*/correct_errors -&gt; mapping -&gt; fill_missing -&gt; derive/conform -&gt; validate/route -&gt; present. This is guidance, not a restriction. Do not use mapping format until the value has finished participating in semantic and business logic.</t>
+      </text>
+    </comment>
+    <comment ref="F9" authorId="0" shapeId="0">
+      <text>
+        <t>Parameters: Lookup, Default, Preserve Unmapped, Case Sensitive, Data Type, Precision, Scale, Format Pattern, Format Case
+Recommended flow: convert_value/type-aware clean_* -&gt; standardize_*/correct_errors -&gt; mapping -&gt; fill_missing -&gt; derive/conform -&gt; validate/route -&gt; present. This is guidance, not a restriction. Do not use mapping format until the value has finished participating in semantic and business logic.</t>
+      </text>
+    </comment>
+    <comment ref="F10" authorId="0" shapeId="0">
+      <text>
+        <t>Parameters: none
+Recommended flow: convert_value/type-aware clean_* -&gt; standardize_*/correct_errors -&gt; mapping -&gt; fill_missing -&gt; derive/conform -&gt; validate/route -&gt; present. This is guidance, not a restriction. Do not use mapping format until the value has finished participating in semantic and business logic.</t>
+      </text>
+    </comment>
+    <comment ref="F11" authorId="0" shapeId="0">
+      <text>
+        <t>Parameters: none
+Recommended flow: convert_value/type-aware clean_* -&gt; standardize_*/correct_errors -&gt; mapping -&gt; fill_missing -&gt; derive/conform -&gt; validate/route -&gt; present. This is guidance, not a restriction. Do not use mapping format until the value has finished participating in semantic and business logic.</t>
+      </text>
+    </comment>
+    <comment ref="F12" authorId="0" shapeId="0">
+      <text>
+        <t>Parameters: none
+Recommended flow: convert_value/type-aware clean_* -&gt; standardize_*/correct_errors -&gt; mapping -&gt; fill_missing -&gt; derive/conform -&gt; validate/route -&gt; present. This is guidance, not a restriction. Do not use mapping format until the value has finished participating in semantic and business logic.</t>
+      </text>
+    </comment>
+    <comment ref="F13" authorId="0" shapeId="0">
+      <text>
+        <t>Parameters: none
+Recommended flow: convert_value/type-aware clean_* -&gt; standardize_*/correct_errors -&gt; mapping -&gt; fill_missing -&gt; derive/conform -&gt; validate/route -&gt; present. This is guidance, not a restriction. Do not use mapping format until the value has finished participating in semantic and business logic.</t>
+      </text>
+    </comment>
+    <comment ref="F14" authorId="0" shapeId="0">
+      <text>
+        <t>Parameters: none
+Recommended flow: convert_value/type-aware clean_* -&gt; standardize_*/correct_errors -&gt; mapping -&gt; fill_missing -&gt; derive/conform -&gt; validate/route -&gt; present. This is guidance, not a restriction. Do not use mapping format until the value has finished participating in semantic and business logic.</t>
+      </text>
+    </comment>
+    <comment ref="F15" authorId="0" shapeId="0">
+      <text>
+        <t>Parameters: Trim, Collapse Whitespace, Case, Blank As Null
+Recommended flow: convert_value/type-aware clean_* -&gt; standardize_*/correct_errors -&gt; mapping -&gt; fill_missing -&gt; derive/conform -&gt; validate/route -&gt; present. This is guidance, not a restriction. Do not use mapping format until the value has finished participating in semantic and business logic.</t>
+      </text>
+    </comment>
+    <comment ref="F16" authorId="0" shapeId="0">
+      <text>
+        <t>Parameters: Precision, Scale
+Recommended flow: convert_value/type-aware clean_* -&gt; standardize_*/correct_errors -&gt; mapping -&gt; fill_missing -&gt; derive/conform -&gt; validate/route -&gt; present. This is guidance, not a restriction. Do not use mapping format until the value has finished participating in semantic and business logic.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>DET Compiler</author>
@@ -1121,6 +1151,21 @@
     <comment ref="D5" authorId="0" shapeId="0">
       <text>
         <t>Parameters: Allow Null</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>DET Compiler</author>
+  </authors>
+  <commentList>
+    <comment ref="T13" authorId="0" shapeId="0">
+      <text>
+        <t>Executable before DET Mapping steps. Enter one scalar SQL expression over fields from declared model inputs, for example UPPER(transaction_description). Do not enter SELECT, FROM, WHERE, joins, aliases, or multiple statements. det validate checks syntax using the configured adapter dialect and verifies column references.</t>
       </text>
     </comment>
   </commentList>
@@ -1927,17 +1972,17 @@
       </c>
       <c r="B40" s="51" t="inlineStr">
         <is>
-          <t>Export package env var, then generate, sync, and lint</t>
+          <t>Generate, synchronize, and lint</t>
         </is>
       </c>
       <c r="C40" s="51" t="inlineStr">
         <is>
-          <t>dbt package refs resolve from your published toolkit Git URL</t>
+          <t>dbt package refs use the public toolkit URL by default</t>
         </is>
       </c>
       <c r="D40" s="51" t="inlineStr">
         <is>
-          <t>export DBT_DATA_ENGINEERING_TOOLKIT_GIT_URL=https://github.com/systemizing-solutions/dbt_data_engineering_toolkit.git; det generate ...; dbt deps; det check ...</t>
+          <t>det generate ...; det check ...; optionally override DBT_DATA_ENGINEERING_TOOLKIT_GIT_URL for a fork or mirror</t>
         </is>
       </c>
     </row>
@@ -9009,14 +9054,14 @@
     <row r="1" ht="28" customHeight="1" s="189">
       <c r="A1" s="56" t="inlineStr">
         <is>
-          <t>DET Source-to-Target Mapping</t>
+          <t>DET Mapping - ordered transformation pipeline</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" s="189">
       <c r="A2" s="60" t="inlineStr">
         <is>
-          <t>Select a model, target, available source field and operation. Put only operation-specific options on DET Parameters.</t>
+          <t>Recommended flow (guidance, not a restriction): scalar ODCS Transform Logic -&gt; convert_value / type-aware clean_* -&gt; standardize_* / correct_errors -&gt; mapping -&gt; fill_missing -&gt; business derivation / target conformance -&gt; validation / routing -&gt; final presentation. Repeat a target field with Step 1, 2, 3... Convert or clean according to target intent; do not clean every source as text. Use mapping format only after semantic and business logic is complete. det validate warns about unusual ordering but permits intentional alternatives.</t>
         </is>
       </c>
     </row>
@@ -10133,8 +10178,8 @@
     <dataValidation sqref="D4:D100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value is out of context" error="Choose a value valid for the selected model, relation, or operation." promptTitle="Context-aware input" prompt="Choose a field from the selected source relation." type="list">
       <formula1>=INDIRECT("_DET_REL_"&amp;SUBSTITUTE(SUBSTITUTE($C4," ","_"),"-","_"))</formula1>
     </dataValidation>
-    <dataValidation sqref="F4:F100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
-      <formula1>'_DET Lists'!$A$2:$A$19</formula1>
+    <dataValidation sqref="F4:F100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Ordered transformation step" prompt="Choose by intent. Recommended: convert/clean -&gt; standardize/correct -&gt; map -&gt; default -&gt; derive/conform -&gt; validate/route -&gt; present. Alternatives are allowed." type="list">
+      <formula1>'_DET Lists'!$A$2:$A$20</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14870,7 +14915,7 @@
     <row r="3" ht="30" customHeight="1" s="189">
       <c r="A3" s="61" t="inlineStr">
         <is>
-          <t>Clean text</t>
+          <t>Convert value</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -14987,7 +15032,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Clean email</t>
+          <t>Clean text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -15089,7 +15134,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Clean phone</t>
+          <t>Clean email</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -15171,7 +15216,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Clean number</t>
+          <t>Clean phone</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -15223,7 +15268,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Clean whole number</t>
+          <t>Clean number</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -15270,7 +15315,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Clean date</t>
+          <t>Clean whole number</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -15317,7 +15362,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Clean timestamp</t>
+          <t>Clean date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -15354,7 +15399,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Clean true/false</t>
+          <t>Clean timestamp</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -15386,7 +15431,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Clean code</t>
+          <t>Clean true/false</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -15408,7 +15453,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Standardise country</t>
+          <t>Clean code</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -15430,7 +15475,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Standardise currency</t>
+          <t>Standardise country</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -15452,7 +15497,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Map values</t>
+          <t>Standardise currency</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -15469,7 +15514,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fill missing</t>
+          <t>Map values</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -15481,7 +15526,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Correct known errors</t>
+          <t>Fill missing</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -15493,7 +15538,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lower case</t>
+          <t>Correct known errors</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -15505,7 +15550,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Upper case</t>
+          <t>Lower case</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -15517,16 +15562,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Upper case</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Pattern</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Title case</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Pattern</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
       <c r="T20" t="inlineStr">
         <is>
           <t>Precision</t>
@@ -15664,7 +15714,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8ce22f79a05d82b337ecfe7087086e2cd216b3f3c9bbeea134d8e716bac4aaf5</t>
+          <t>9cf184d87d656fdec8fe3ae1bcf6d1d769f84995baf0fcc1ee89b6ede9e5277f</t>
         </is>
       </c>
     </row>
@@ -15700,7 +15750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO12"/>
+  <dimension ref="A1:AQ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15776,135 +15826,145 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>_DET_OP_convert_value</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>_DET_OP_copy</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>_DET_OP_correct_errors</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>_DET_OP_fill_missing</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>_DET_OP_is_between</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>_DET_OP_is_email</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>_DET_OP_is_in_list</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>_DET_OP_is_positive</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>_DET_OP_lower</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>_DET_OP_map_values</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>_DET_OP_no_future_date</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>_DET_OP_regex_match</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>_DET_OP_required</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>_DET_OP_rule_compare</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>_DET_OP_standardize_country</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>_DET_OP_standardize_currency</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>_DET_OP_title</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>_DET_OP_unique</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>_DET_OP_upper</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>_DET_REL_customer_account_mart</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>_DET_REL_raw_accounts</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>_DET_REL_raw_customers</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>_DET_REL_stg_customers</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>_DET_VALUE_clean_code_case</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>_DET_VALUE_clean_text_case</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>_DET_VALUE_convert_value_data_type</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
         <is>
           <t>_DET_VALUE_map_values_data_type</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>_DET_VALUE_map_values_format_case</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>_DET_VALUE_rule_compare_operator</t>
         </is>
@@ -15961,101 +16021,111 @@
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Lookup</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Fill Value</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Minimum</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Allow Null</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Values</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Allow Null</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr">
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
         <is>
           <t>Lookup</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr">
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>Pattern</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr">
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Operator</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr">
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>_det_invocation_id</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>account_id</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>account_id</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>_det_invocation_id</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>preserve</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>preserve</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>preserve</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>=</t>
         </is>
@@ -16092,72 +16162,82 @@
           <t>Collapse Whitespace</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Case Sensitive</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Maximum</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Allow Null</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>Compare To</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>_det_loaded_at</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>account_tier</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>customer_id</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>_det_loaded_at</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>lower</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>lower</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>lower</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>!=</t>
         </is>
@@ -16184,67 +16264,77 @@
           <t>Case</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>Inclusive</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Case Sensitive</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Preserve Unmapped</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>Allow Null</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>_det_rejections</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
         <is>
           <t>lifetime_value</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>customer_name</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AK4" t="inlineStr">
         <is>
           <t>_det_source_system</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>upper</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>upper</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>upper</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>&lt;&gt;</t>
         </is>
@@ -16271,42 +16361,47 @@
           <t>Blank As Null</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Allow Null</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>Case Sensitive</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
         <is>
           <t>_det_source_system</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AK5" t="inlineStr">
         <is>
           <t>_det_warnings</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>&lt;</t>
         </is>
@@ -16323,32 +16418,37 @@
           <t>account_id</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>account_id</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>status_code</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AK6" t="inlineStr">
         <is>
           <t>account_id</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>&lt;=</t>
         </is>
@@ -16365,27 +16465,32 @@
           <t>customer_id</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>account_tier</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>customer_id</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>&gt;</t>
         </is>
@@ -16402,22 +16507,22 @@
           <t>customer_name</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>Scale</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
         <is>
           <t>customer_id</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>customer_name</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
@@ -16434,17 +16539,17 @@
           <t>email</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>Format Pattern</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
         <is>
           <t>customer_name</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AK9" t="inlineStr">
         <is>
           <t>email</t>
         </is>
@@ -16461,17 +16566,17 @@
           <t>status_label</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>Format Case</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>status_label</t>
         </is>
@@ -16483,7 +16588,7 @@
           <t>lifetime_value</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
+      <c r="AH11" t="inlineStr">
         <is>
           <t>lifetime_value</t>
         </is>
@@ -16495,7 +16600,7 @@
           <t>status_label</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
+      <c r="AH12" t="inlineStr">
         <is>
           <t>status_label</t>
         </is>
@@ -16564,8 +16669,8 @@
     <col hidden="1" outlineLevel="1" width="13" customWidth="1" style="189" min="17" max="17"/>
     <col hidden="1" outlineLevel="1" width="13" customWidth="1" style="189" min="18" max="18"/>
     <col hidden="1" outlineLevel="1" width="13" customWidth="1" style="189" min="19" max="19"/>
-    <col hidden="1" outlineLevel="1" width="13" customWidth="1" style="189" min="20" max="20"/>
-    <col hidden="1" outlineLevel="1" width="21.6640625" customWidth="1" style="2" min="21" max="21"/>
+    <col width="42" customWidth="1" style="189" min="20" max="20"/>
+    <col width="32" customWidth="1" style="2" min="21" max="21"/>
     <col hidden="1" outlineLevel="1" width="27.33203125" customWidth="1" style="2" min="22" max="22"/>
     <col hidden="1" outlineLevel="1" width="15.5" customWidth="1" style="2" min="23" max="37"/>
     <col hidden="1" outlineLevel="1" width="13" customWidth="1" style="189" min="24" max="24"/>
@@ -20794,7 +20899,16 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="29">
+  <dataValidations count="32">
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
     <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
       <formula1>'_DET Lists'!$U$2:$U$4</formula1>
     </dataValidation>
@@ -20884,6 +20998,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -20915,8 +21030,8 @@
     <col hidden="1" outlineLevel="1" width="13" customWidth="1" style="189" min="17" max="17"/>
     <col hidden="1" outlineLevel="1" width="13" customWidth="1" style="189" min="18" max="18"/>
     <col hidden="1" outlineLevel="1" width="13" customWidth="1" style="189" min="19" max="19"/>
-    <col hidden="1" outlineLevel="1" width="13" customWidth="1" style="189" min="20" max="20"/>
-    <col hidden="1" outlineLevel="1" width="21.6640625" customWidth="1" style="2" min="21" max="21"/>
+    <col width="42" customWidth="1" style="189" min="20" max="20"/>
+    <col width="32" customWidth="1" style="2" min="21" max="21"/>
     <col hidden="1" outlineLevel="1" width="27.33203125" customWidth="1" style="2" min="22" max="22"/>
     <col hidden="1" outlineLevel="1" width="15.5" customWidth="1" style="2" min="23" max="37"/>
     <col hidden="1" outlineLevel="1" width="13" customWidth="1" style="189" min="24" max="24"/>
@@ -25097,7 +25212,16 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="40">
+  <dataValidations count="43">
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
     <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
       <formula1>'_DET Lists'!$U$2:$U$4</formula1>
     </dataValidation>
@@ -25220,6 +25344,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_multi_source_sample.xlsx
+++ b/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_multi_source_sample.xlsx
@@ -1,36 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fundamentals" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schema stg_customers" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quality" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLA" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Servers" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Custom Properties" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Models" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Model Inputs" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Sources" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Source Schema" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Mapping" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Parameters" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Relationships" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operational Validation" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operational Parameters" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Lookups" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Build" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_DET Lists" sheetId="24" state="veryHidden" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_DET Metadata" sheetId="25" state="veryHidden" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_DET Context" sheetId="26" state="veryHidden" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_DET Raw ODCS" sheetId="27" state="veryHidden" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schema customer_account_mart" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fundamentals" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Schema stg_customers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Relationships" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Quality" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Support" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Team" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Roles" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="SLA" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Servers" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Pricing" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Custom Properties" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="DET Models" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="DET Model Inputs" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="DET Sources" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="DET Source Schema" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="DET Mapping" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="DET Parameters" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="DET Relationships" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Operational Validation" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Operational Parameters" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="DET Lookups" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="DET Build" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="_DET Lists" sheetId="24" state="veryHidden" r:id="rId24"/>
+    <sheet name="_DET Metadata" sheetId="25" state="veryHidden" r:id="rId25"/>
+    <sheet name="_DET Context" sheetId="26" state="veryHidden" r:id="rId26"/>
+    <sheet name="_DET Raw ODCS" sheetId="27" state="veryHidden" r:id="rId27"/>
+    <sheet name="Schema customer_account_mart" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames>
     <definedName name="apiVersion">Fundamentals!$C$5</definedName>
@@ -1783,7 +1783,7 @@
     <row r="31" ht="16" customHeight="1" s="189">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>dbt_data_engineering_toolkit v4.1.1 workflow</t>
+          <t>dbt_data_engineering_toolkit v5.0.0 workflow</t>
         </is>
       </c>
       <c r="E31" s="13" t="n"/>
@@ -14582,7 +14582,7 @@
       </c>
       <c r="B8" s="207" t="inlineStr">
         <is>
-          <t>v4.1.1</t>
+          <t>5.0.0</t>
         </is>
       </c>
       <c r="C8" s="193" t="inlineStr">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="B4" s="193" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>5.0.0</t>
         </is>
       </c>
     </row>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="B5" s="193" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>5.0.0</t>
         </is>
       </c>
     </row>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="B6" s="193" t="inlineStr">
         <is>
-          <t>4.1.1</t>
+          <t>5.0.0</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9cf184d87d656fdec8fe3ae1bcf6d1d769f84995baf0fcc1ee89b6ede9e5277f</t>
+          <t>d8ff7534071a935c3c1cba26962e46c8365474f8d2bdc38aaa3d76ac03a4c6c5</t>
         </is>
       </c>
     </row>
@@ -20899,7 +20899,10 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="32">
+  <dataValidations count="33">
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
     <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
       <formula1>'_DET Lists'!$U$2:$U$4</formula1>
     </dataValidation>
@@ -25212,7 +25215,10 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="43">
+  <dataValidations count="44">
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
     <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
       <formula1>'_DET Lists'!$U$2:$U$4</formula1>
     </dataValidation>

--- a/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_multi_source_sample.xlsx
+++ b/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_multi_source_sample.xlsx
@@ -1783,7 +1783,7 @@
     <row r="31" ht="16" customHeight="1" s="189">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>dbt_data_engineering_toolkit v5.0.0 workflow</t>
+          <t>dbt_data_engineering_toolkit v5.0.1 workflow</t>
         </is>
       </c>
       <c r="E31" s="13" t="n"/>
@@ -14582,7 +14582,7 @@
       </c>
       <c r="B8" s="207" t="inlineStr">
         <is>
-          <t>5.0.0</t>
+          <t>5.0.1</t>
         </is>
       </c>
       <c r="C8" s="193" t="inlineStr">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="B4" s="193" t="inlineStr">
         <is>
-          <t>5.0.0</t>
+          <t>5.0.1</t>
         </is>
       </c>
     </row>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="B5" s="193" t="inlineStr">
         <is>
-          <t>5.0.0</t>
+          <t>5.0.1</t>
         </is>
       </c>
     </row>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="B6" s="193" t="inlineStr">
         <is>
-          <t>5.0.0</t>
+          <t>5.0.1</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>d8ff7534071a935c3c1cba26962e46c8365474f8d2bdc38aaa3d76ac03a4c6c5</t>
+          <t>dbfd0d014950db40827ad9ff185c82576017f3cf7b601649207b59f39be8b713</t>
         </is>
       </c>
     </row>
@@ -20899,7 +20899,10 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="33">
+  <dataValidations count="34">
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
     <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
       <formula1>'_DET Lists'!$U$2:$U$4</formula1>
     </dataValidation>
@@ -25215,7 +25218,10 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="44">
+  <dataValidations count="45">
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
     <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
       <formula1>'_DET Lists'!$U$2:$U$4</formula1>
     </dataValidation>

--- a/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_multi_source_sample.xlsx
+++ b/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_multi_source_sample.xlsx
@@ -1783,7 +1783,7 @@
     <row r="31" ht="16" customHeight="1" s="189">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>dbt_data_engineering_toolkit v5.0.1 workflow</t>
+          <t>dbt_data_engineering_toolkit v6.0.0 workflow</t>
         </is>
       </c>
       <c r="E31" s="13" t="n"/>
@@ -14582,7 +14582,7 @@
       </c>
       <c r="B8" s="207" t="inlineStr">
         <is>
-          <t>5.0.1</t>
+          <t>6.0.0</t>
         </is>
       </c>
       <c r="C8" s="193" t="inlineStr">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="B4" s="193" t="inlineStr">
         <is>
-          <t>5.0.1</t>
+          <t>6.0.0</t>
         </is>
       </c>
     </row>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="B5" s="193" t="inlineStr">
         <is>
-          <t>5.0.1</t>
+          <t>6.0.0</t>
         </is>
       </c>
     </row>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="B6" s="193" t="inlineStr">
         <is>
-          <t>5.0.1</t>
+          <t>6.0.0</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>dbfd0d014950db40827ad9ff185c82576017f3cf7b601649207b59f39be8b713</t>
+          <t>01ed9867ee80cfec6cdedde409b91b1bfe902129513d175eec91ae48299eb186</t>
         </is>
       </c>
     </row>
@@ -20899,7 +20899,10 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="34">
+  <dataValidations count="35">
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
     <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
       <formula1>'_DET Lists'!$U$2:$U$4</formula1>
     </dataValidation>
@@ -25218,7 +25221,10 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="45">
+  <dataValidations count="46">
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
     <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
       <formula1>'_DET Lists'!$U$2:$U$4</formula1>
     </dataValidation>
